--- a/data/detail_data.xlsx
+++ b/data/detail_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kouro\Desktop\map-main (3)\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70B8D1F-E7A0-49DE-A55A-B32FAC897E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC610B7A-5298-490E-8CE6-181C92A71543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9360" yWindow="1500" windowWidth="16230" windowHeight="13950" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ΕΠ ΥΜΕΠΕΡΑΑ" sheetId="1" r:id="rId1"/>
@@ -2563,8 +2563,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="2" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="39" customWidth="1"/>
     <col min="5" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
@@ -2644,271 +2643,271 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
+    <row r="3" spans="1:15" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="C3" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
+      <c r="G3" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
     </row>
     <row r="4" spans="1:15" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="B4" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="C4" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
+      <c r="G4" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="5" spans="1:15" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="B5" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="C5" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>202</v>
-      </c>
+      <c r="F5" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B6" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="C6" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="G6" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="O6" s="3"/>
+      <c r="J6" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
     </row>
     <row r="7" spans="1:15" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="B7" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="C7" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="I7" s="5" t="s">
+      <c r="G7" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-    </row>
-    <row r="8" spans="1:15" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="J7" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="O7" s="3"/>
+    </row>
+    <row r="8" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="O8" s="3"/>
+      <c r="C8" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/detail_data.xlsx
+++ b/data/detail_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kouro\Desktop\map-main (3)\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC610B7A-5298-490E-8CE6-181C92A71543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70B8D1F-E7A0-49DE-A55A-B32FAC897E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9360" yWindow="1500" windowWidth="16230" windowHeight="13950" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ΕΠ ΥΜΕΠΕΡΑΑ" sheetId="1" r:id="rId1"/>
@@ -2563,7 +2563,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="3" width="18" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="39" customWidth="1"/>
     <col min="5" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
@@ -2643,271 +2644,271 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="3" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
+      <c r="G3" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
     </row>
     <row r="4" spans="1:15" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="B4" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="C4" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>202</v>
-      </c>
+      <c r="G4" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
     </row>
     <row r="5" spans="1:15" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B5" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="C5" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="O5" s="3"/>
+      <c r="F5" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="6" spans="1:15" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="B6" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="C6" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="I6" s="5" t="s">
+      <c r="G6" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="J6" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
+      <c r="J6" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="O6" s="3"/>
     </row>
     <row r="7" spans="1:15" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+    </row>
+    <row r="8" spans="1:15" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="N7" s="3" t="s">
+      <c r="N8" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="O7" s="3"/>
-    </row>
-    <row r="8" spans="1:15" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>1</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
+      <c r="O8" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
